--- a/FST16_Assemblies_Export_DL.xlsx
+++ b/FST16_Assemblies_Export_DL.xlsx
@@ -131,8 +131,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssembliesTable" displayName="AssembliesTable" ref="A1:E3" headerRowCount="1">
-  <autoFilter ref="A1:E3"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssembliesTable" displayName="AssembliesTable" ref="A1:E5" headerRowCount="1">
+  <autoFilter ref="A1:E5"/>
   <tableColumns count="5">
     <tableColumn id="1" name="Assembly Version"/>
     <tableColumn id="2" name="Date"/>
@@ -433,10 +433,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E3"/>
+  <dimension ref="A1:E5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="21" customWidth="1" min="1" max="1"/>
+    <col width="25" customWidth="1" min="1" max="1"/>
     <col width="24" customWidth="1" min="2" max="2"/>
     <col width="21" customWidth="1" min="3" max="3"/>
     <col width="45" customWidth="1" min="4" max="4"/>
@@ -478,11 +478,11 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2026-10-07 11:14:17</t>
+          <t>2026-10-13 20:44:24</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1850.62</v>
+        <v>1801.6</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
@@ -495,8 +495,8 @@
 UP_01: vFST15
 UP_02: vFST15
 UP_03: vFST15
-Inner Bearing: v61816
-Outer Bearing: v61815
+Inner Bearing: v61815
+Outer Bearing: v61816
 Seal: v95X110X9 HMSA10 V</t>
         </is>
       </c>
@@ -533,6 +533,66 @@
         </is>
       </c>
     </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>2.0 (Without Support)</t>
+        </is>
+      </c>
+      <c r="B4" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:49:23</t>
+        </is>
+      </c>
+      <c r="C4" s="1" t="n">
+        <v>648.28</v>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>This assembly has the objective of having a comparative analysis with the FST15 design with the same features, focusing in the new v2.0 transmission</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>TD: v2.0
+UP_01: v2.0 (without supports)
+UP_02: v2.0 (with all features)
+Inner Bearing: v61816
+Outer Bearing: v61816
+Seal: v85X100X9 HMSA10 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>FST15 (Without Support)</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-13 20:44:41</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>856.61</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>This assembly has the objective of having a comparative baseline without the supports</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>UP_01: vFST15 (without supports)
+UP_02: vFST15 (with all features)
+UP_03: vFST15
+Inner Bearing: v61815
+Outer Bearing: v61816
+Seal: v95X110X9 HMSA10 V</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <tableParts count="1">

--- a/FST16_Assemblies_Export_DL.xlsx
+++ b/FST16_Assemblies_Export_DL.xlsx
@@ -473,54 +473,23 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>FST15</t>
+          <t>1.0</t>
         </is>
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>2026-10-13 20:44:24</t>
+          <t>2026-10-12 22:02:36</t>
         </is>
       </c>
       <c r="C2" s="1" t="n">
-        <v>1801.6</v>
+        <v>1690.22</v>
       </c>
       <c r="D2" s="2" t="inlineStr">
         <is>
-          <t>FST15 Baseline</t>
+          <t>The first iteration for the new motors where the bearings sit right on top of the seal</t>
         </is>
       </c>
       <c r="E2" s="2" t="inlineStr">
-        <is>
-          <t>HB_01: vFST15
-UP_01: vFST15
-UP_02: vFST15
-UP_03: vFST15
-Inner Bearing: v61815
-Outer Bearing: v61816
-Seal: v95X110X9 HMSA10 V</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="1" t="inlineStr">
-        <is>
-          <t>1.0</t>
-        </is>
-      </c>
-      <c r="B3" s="1" t="inlineStr">
-        <is>
-          <t>2026-10-12 22:02:36</t>
-        </is>
-      </c>
-      <c r="C3" s="1" t="n">
-        <v>1690.22</v>
-      </c>
-      <c r="D3" s="2" t="inlineStr">
-        <is>
-          <t>The first iteration for the new motors where the bearings sit right on top of the seal</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>TD: v1.2
 HB_01: v1
@@ -533,26 +502,26 @@
         </is>
       </c>
     </row>
-    <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+    <row r="3">
+      <c r="A3" s="1" t="inlineStr">
         <is>
           <t>2.0 (Without Support)</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B3" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:49:23</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C3" s="1" t="n">
         <v>648.28</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D3" s="2" t="inlineStr">
         <is>
           <t>This assembly has the objective of having a comparative analysis with the FST15 design with the same features, focusing in the new v2.0 transmission</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>TD: v2.0
 UP_01: v2.0 (without supports)
@@ -563,26 +532,26 @@
         </is>
       </c>
     </row>
-    <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
         <is>
           <t>FST15 (Without Support)</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B4" s="1" t="inlineStr">
         <is>
           <t>2026-10-13 20:44:41</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
+      <c r="C4" s="1" t="n">
         <v>856.61</v>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>This assembly has the objective of having a comparative baseline without the supports</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>UP_01: vFST15 (without supports)
 UP_02: vFST15 (with all features)
@@ -590,6 +559,37 @@
 Inner Bearing: v61815
 Outer Bearing: v61816
 Seal: v95X110X9 HMSA10 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="inlineStr">
+        <is>
+          <t>FST15</t>
+        </is>
+      </c>
+      <c r="B5" s="1" t="inlineStr">
+        <is>
+          <t>2026-10-18 10:53:30</t>
+        </is>
+      </c>
+      <c r="C5" s="1" t="n">
+        <v>2220.16</v>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>FST15 Baseline</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>HB_01: vFST15
+UP_01: vFST15
+UP_02: vFST15
+UP_03: vFST15
+Inner Bearing: v61815
+Outer Bearing: v61815
+Seal: v85X100X9 HMSA10 V</t>
         </is>
       </c>
     </row>

--- a/FST16_Assemblies_Export_DL.xlsx
+++ b/FST16_Assemblies_Export_DL.xlsx
@@ -46,11 +46,8 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -128,20 +125,6 @@
     </indexedColors>
   </colors>
 </styleSheet>
-</file>
-
-<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="AssembliesTable" displayName="AssembliesTable" ref="A1:E5" headerRowCount="1">
-  <autoFilter ref="A1:E5"/>
-  <tableColumns count="5">
-    <tableColumn id="1" name="Assembly Version"/>
-    <tableColumn id="2" name="Date"/>
-    <tableColumn id="3" name="Total Weight (g)"/>
-    <tableColumn id="4" name="Description"/>
-    <tableColumn id="5" name="Part Configuration"/>
-  </tableColumns>
-  <tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
-</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -471,25 +454,25 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="1" t="inlineStr">
+      <c r="A2" t="inlineStr">
         <is>
           <t>1.0</t>
         </is>
       </c>
-      <c r="B2" s="1" t="inlineStr">
+      <c r="B2" t="inlineStr">
         <is>
           <t>2026-10-12 22:02:36</t>
         </is>
       </c>
-      <c r="C2" s="1" t="n">
+      <c r="C2" t="n">
         <v>1690.22</v>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="1" t="inlineStr">
         <is>
           <t>The first iteration for the new motors where the bearings sit right on top of the seal</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="1" t="inlineStr">
         <is>
           <t>TD: v1.2
 HB_01: v1
@@ -503,25 +486,25 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="1" t="inlineStr">
+      <c r="A3" t="inlineStr">
         <is>
           <t>2.0 (Without Support)</t>
         </is>
       </c>
-      <c r="B3" s="1" t="inlineStr">
+      <c r="B3" t="inlineStr">
         <is>
           <t>2026-10-13 20:49:23</t>
         </is>
       </c>
-      <c r="C3" s="1" t="n">
+      <c r="C3" t="n">
         <v>648.28</v>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D3" s="1" t="inlineStr">
         <is>
           <t>This assembly has the objective of having a comparative analysis with the FST15 design with the same features, focusing in the new v2.0 transmission</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E3" s="1" t="inlineStr">
         <is>
           <t>TD: v2.0
 UP_01: v2.0 (without supports)
@@ -533,25 +516,25 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="1" t="inlineStr">
+      <c r="A4" t="inlineStr">
         <is>
           <t>FST15 (Without Support)</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
+      <c r="B4" t="inlineStr">
         <is>
           <t>2026-10-13 20:44:41</t>
         </is>
       </c>
-      <c r="C4" s="1" t="n">
+      <c r="C4" t="n">
         <v>856.61</v>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="D4" s="1" t="inlineStr">
         <is>
           <t>This assembly has the objective of having a comparative baseline without the supports</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="E4" s="1" t="inlineStr">
         <is>
           <t>UP_01: vFST15 (without supports)
 UP_02: vFST15 (with all features)
@@ -563,30 +546,31 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="1" t="inlineStr">
+      <c r="A5" t="inlineStr">
         <is>
           <t>FST15</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
+      <c r="B5" t="inlineStr">
         <is>
           <t>2026-10-18 10:53:30</t>
         </is>
       </c>
-      <c r="C5" s="1" t="n">
-        <v>2220.16</v>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="C5" t="n">
+        <v>2270.05</v>
+      </c>
+      <c r="D5" s="1" t="inlineStr">
         <is>
           <t>FST15 Baseline</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="E5" s="1" t="inlineStr">
         <is>
           <t>HB_01: vFST15
 UP_01: vFST15
 UP_02: vFST15
 UP_03: vFST15
+UP_05: vFST15
 Inner Bearing: v61815
 Outer Bearing: v61815
 Seal: v85X100X9 HMSA10 V</t>
@@ -595,8 +579,5 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <tableParts count="1">
-    <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </tableParts>
 </worksheet>
 </file>